--- a/latest.xlsx
+++ b/latest.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -510,7 +510,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06T08:20:03+08:00</t>
+          <t>2026-10-07T08:20:03+08:00</t>
         </is>
       </c>
     </row>

--- a/latest.xlsx
+++ b/latest.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -510,7 +510,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T08:20:03+08:00</t>
+          <t>2026-10-08T08:20:03+08:00</t>
         </is>
       </c>
     </row>
